--- a/SINGLE HADITH CONTENT/missing_input/[V1] RIYAZUS SALEHIN-(HBD)-BANGLA_missing.xlsx
+++ b/SINGLE HADITH CONTENT/missing_input/[V1] RIYAZUS SALEHIN-(HBD)-BANGLA_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C163"/>
+  <dimension ref="A1:C192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3187,6 +3187,499 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>وَعَنهُ رضي الله عنه، قَالَ: جَاءَ رَجُلٌ إِلَى رَسُولِ اللهِ صلى الله عليه وسلم، فَقَالَ: يَا رَسُولَ الله، مَنْ أحَقُّ النَّاسِ بِحُسْنِ صَحَابَتِي ؟ قَالَ: «أُمُّكَ»قَالَ : ثُمَّ مَنْ ؟ قَالَ: «أُمُّكَ»، قَالَ : ثُمَّ مَنْ ؟ قَالَ : «أُمُّكَ»، قَالَ : ثُمَّ مَنْ ؟ قَالَ: «أبُوكَ». مُتَّفَقٌ عَلَيهِوفي رواية : يَا رَسُولَ اللهِ صلى الله عليه وسلم، مَنْ أَحَقُّ بحُسْنِ الصُّحْبَةِ ؟ قَالَ: أُمُّكَ، ثُمَّ أُمُّكَ، ثُمَّ أُمُّكَ، ثُمَّ أَبَاكَ، ثُمَّ أدْنَاكَ أدْنَاكَوالصَّحابة « بمعنى : الصُّحبةِ . وقوله : » ثُمَّ أباك « هَكَذا هو منصوب بفعلٍ محذوف،ٍ أي ثم برَّ أَباكوفي رواية : » ثُمَّ أَبُوكَ « وهذا واضِح .</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>আবূ হুরায়রা (রাঃ) থেকেই বর্ণিত, তিনি বলেন, একটি লোক রাসূলুল্লাহ (صلى الله عليه وسلم)-এর নিকট এসে জিজ্ঞেস করল, ’হে আল্লাহর রাসূল! আমার কাছ থেকে সদ্ব্যবহার পাওয়ার বেশী হকদার কে?’ তিনি বললেন, ’’তোমার মা।’’ সে বলল, ’তারপর কে?’ তিনি বললেন, ’’তোমার মা।’’ সে বলল, ’তারপর কে?’ তিনি বললেন, ’’তোমার মা।’’ সে বলল, ’তারপর কে?’ তিনি বললেন, ’’তোমার বাপ।’’ (বুখারী ও মুসলিম) [১] অন্য এক বর্ণনায় আছে, ’হে আল্লাহর রাসূল! সদ্ব্যবহার পাওয়ার বেশী হকদার কে?’ তিনি বললেন, ’’তোমার মা, তারপর তোমার মা, তারপর তোমার মা, তারপর তোমার বাপ, তারপর যে তোমার সবচেয়ে নিকটবর্তী।’’</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>وَعَنهُ، عَنِ النَّبيِّ صلى الله عليه وسلم، قَالَ: «رَغِمَ أَنفُ، ثُمَّ رَغِمَ أنْفُ، ثُمَّ رَغِمَ أنْفُ مَنْ أدْرَكَ أبَويهِ عِنْدَ الكِبَرِ، أَحَدهُما أَوْ كِليهمَا فَلَمْ يَدْخُلِ الجَنَّةَ». رواه مسلم</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>আবূ হুরায়রা (রাঃ) থেকেই বর্ণিত, নবী (صلى الله عليه وسلم) বলেন, ’’তার নাক ধূলিধূসরিত হোক, অতঃপর তার নাক ধূলিধূসরিত হোক, অতঃপর তার নাক ধূলিধূসরিত হোক, যে ব্যক্তি তার পিতা-মাতাকে বৃদ্ধ অবস্থায় পেল; একজনকে অথবা দু’জনকেই। অতঃপর সে (তাদের খিদমত ক’রে) জান্নাত যেতে পারল না।’’ (মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>وَعَنهُ رضي الله عنه : أَنَّ رَجُلاً قَالَ : يَا رَسُولَ اللهِ صلى الله عليه وسلم، إنَّ لِي قَرَابةً أصِلُهُمْ وَيَقْطَعُوني، وَأُحْسِنُ إلَيْهِمْ وَيُسِيئُونَ إلَيَّ، وَأحْلَمُ عَنْهُمْ وَيَجْهَلُونَ عَلَيَّ، فَقَالَ: «لَئِنْ كُنْتَ كَمَا قُلْتَ، فَكأنَّمَا تُسِفُّهُمْ الْمَلَّ، وَلاَ يَزَالُ مَعَكَ مِنَ اللهِ ظَهِيرٌ عَلَيْهِمْ مَا دُمْتَ عَلَى ذَلِكَ». رواه مسلموتسِفُّهُمْ « بضم التاءِ وآسرِ السين المهملةِ وتشديد الفاءِ . » والمَلُّ « بفتحِ الميم ، وتشديد اللام وهوالرَّماد الحارُّ : أَيْ آأَنَّمَا تُطْعِمُهُمْ الرَّماد الحارَّ وهُو تَشبِيهٌ لِما يلْحَقُهمْ مِنَ الإِثم بِما يَلْحقُ آآِلَ الرَّمادِ مِنَ الإِثمِ، ولا شئَ على المُحْسِنِ إِلَيْهِمْ ، لَكِنْ يَنَالهُمْ إِثْمٌ عَظَيمٌ بَتَقْصيِرهِم في حَقِه ، وإِدخَالِهِمُ الأَذَى عَلَيْهِ، واللَّه أعلم.</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>আবূ হুরায়রা (রাঃ) থেকেই বর্ণিত, এক ব্যক্তি বলল, ’হে আল্লাহর রাসূল! আমার কিছু আত্মীয় আছে, আমি তাদের সাথে আত্মীয়তা বজায় রাখি, আর তারা ছিন্ন করে। আমি তাদের সাথে সদ্ব্যবহার করি, আর তারা আমার সাথে দুর্ব্যবহার করে। তারা কষ্ট দিলে আমি সহ্য করি, আর তারা আমার সাথে মূর্খের আচরণ করে।’ তিনি বললেন, ’’যদি তা-ই হয়, তাহলে তুমি যেন তাদের মুখে গরম ছাই নিক্ষেপ করছ (অর্থাৎ এ কাজে তারা গোনাহগার হয়।) এবং তোমার সাথে আল্লাহর পক্ষ থেকে তাদের বিরুদ্ধে সাহায্যকারী থাকবে; যতক্ষণ পর্যন্ত তুমি এর উপর অনড় থাকবে।’’ (মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>وَعَن أَنَسٍ رضي الله عنه : أَنَّ رَسُولَ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم، قَالَ : «مَن أحَبَّ أنْ يُبْسَطَ لَهُ فِي رِزْقِهِ، ويُنْسأَ لَهُ فِي أثَرِهِ، فَلْيَصِلْ رَحِمَهُ». مُتَّفَقٌ عَلَيهِ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেন, ’’যে ব্যক্তি চায় যে, তার রুযী (জীবিকা) প্রশস্ত হোক এবং আয়ু বৃদ্ধি হোক, সে যেন তার আত্মীয়তার সম্পর্ক অক্ষুণ্ণ রাখে।’’ (বুখারী ও মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>عَن أَنَسٍ رضي الله عنه، قَالَ : كَانَ أَبُو طَلْحَةَ رضي الله عنه أكْثَرَ الأنْصَار بالمَدِينَةِ مَالاً مِنْ نَخْل، وَكَانَ أَحَبُّ أمْوالِهِ إِلَيْه بَيْرُحَاء، وَكَانتْ مُسْتَقْبلَةَ المَسْجِدِ وَكَانَ رَسُول الله صلى الله عليه وسلم يَدْخُلُهَا وَيَشْرَبُ مِنْ مَاءٍ فِيهَا طَيِّب . قَالَ أنَسٌ : فَلَمَّا نَزَلَتْ هذِهِ الآيةُ: ﴿ لن تنالوا البر حتى تنفقوا مما تحبون﴾ [ال عمران: ٩٢] قام أَبُو طَلْحَةَ إِلَى رَسُولِ الله صلى الله عليه وسلم، فَقَالَ : يَا رَسُولَ الله، إنَّ الله تَعَالَى أنْزَلَ عَلَيْكَ : ﴿ لن تنالوا البر حتى تنفقوا مما تحبون﴾ وَإنَّ أَحَبَّ مَالِي إِلَيَّ بَيْرُحَاءُ، وَإنَّهَا صَدَقَةٌ للهِ تَعَالَى، أرْجُو بِرَّهَا، وَذُخْرَهَا عِنْدَ الله تَعَالَى، فَضَعْهَا يَا رَسُول الله حَيْثُ أرَاكَ الله، فَقَالَ رَسُولُ الله صلى الله عليه وسلم: بَخ ! ذلِكَ مَالٌ رَابحٌ، ذلِكَ مَالٌ رَابحٌ، وقَدْ سَمِعْتُ مَا قُلْتَ، وَإنِّي أرَى أنْ تَجْعَلَهَا في الأقْرَبينَ»، فَقَالَ أَبُو طَلْحَةَ : أفْعَلُ يَا رَسُولَ الله، فَقَسَّمَهَا أَبُو طَلْحَةَ في أقَارِبِهِ، وبَنِي عَمِّهِ . مُتَّفَقٌ عَلَيهِ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>মদীনার আনসারীগণের মধ্যে আবূ তালহা (রাঃ) সবচেয়ে অধিক খেজুর বাগানের মালিক ছিলেন। মসজিদে নববীর নিকটবর্তী বায়রুহা নামক বাগানটি তাঁর কাছে অধিক প্রিয় ছিল। রাসূলুল্লাহ (صلى الله عليه وسلم) তাঁর বাগানে প্রবেশ করে সুপেয় পানি পান করতেন। আনাস (রাঃ) বলেন, যখন এ আয়াত অবতীর্ণ হল; যার অর্থ, ’’তোমরা কখনও পুণ্য লাভ করতে পারবে না, যতক্ষণ না তোমাদের প্রিয় জিনিস আল্লাহর পথে ব্যয় করেছ।’’ (আলে ইমরান ৯২আয়াত) তখন আবূ তালহা (রাঃ) আল্লাহর রাসূল (صلى الله عليه وسلم)-এর নিকট গিয়ে বললেন, ’ইয়া রাসূলুল্লাহ! আল্লাহ আপনার উপর (আয়াত) অবতীর্ণ করে বলেছেন, ’’তোমরা কখনও পুণ্য লাভ করতে পারবে না, যতক্ষণ না তোমাদের প্রিয় জিনিস আল্লাহর পথে ব্যয় করেছ।’’ আর বায়রুহা বাগানটি আমার নিকট সবচেয়ে প্রিয়। এটি আল্লাহর নামে সদকাহ করা হল। আমি এর কল্যাণ কামনা করি এবং তা আল্লাহর নিকট আমার জন্য জমা হয়ে থাকবে। কাজেই আপনি যাকে দান করা ভাল মনে করেন, তাকে দান করে দিন।’ তখন রাসূলুল্লাহ (صلى الله عليه وسلم) বললেন, ’’আরে! এ হচ্ছে লাভজনক সম্পদ। এ হচ্ছে লাভজনক সম্পদ। তুমি যা বলেছ, তা শুনেছি। আমি মনে করি,তুমি তোমার আপন-জনদের মধ্যে তা বণ্টন করে দাও।’’ আবূ তালহা (রাঃ) বললেন, ’ইয়া রাসূলাল্লাহ! আমি তাই করব।’ তারপর তিনি তাঁর আত্মীয়-স্বজন, আপন চাচার বংশধরদের মধ্যে তা বণ্টন করে দিলেন। (বুখারী-মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>وَعَن عَبدِ اللهِ بنِ عَمرِو بنِ العَاصِ رَضِيَ اللهُ عَنهُمَا، قَالَ : أقبلَ رَجُلٌ إِلَى نَبيِّ الله صلى الله عليه وسلم، فَقَالَ : أُبَايِعُكَ عَلَى الهِجْرَةِ وَالجِهَادِ أَبْتَغي الأَجْرَ مِنَ الله تَعَالَى . قَالَ: «فَهَلْ لَكَ مِنْ وَالِدَيْكَ أحَدٌ حَيٌّ؟» قَالَ : نَعَمْ، بَلْ كِلاهُمَا. قَالَ: «فَتَبْتَغي الأجْرَ مِنَ الله تَعَالَى؟» قَالَ : نَعَمْ. قَالَ: «فارْجِعْ إِلَى وَالِدَيْكَ، فَأحْسِنْ صُحْبَتَهُمَا». مُتَّفَقٌ عَلَيهِ، وهذا لَفْظُ مسلِم .وفي رواية لَهُمَا: جَاءَ رَجُلٌ فَاسْتَأذَنَهُ في الجِهَادِ، فقَالَ: أحَيٌّ وَالِداكَ ؟ قَالَ : نَعَمْ، قَالَ: فَفيهِمَا فَجَاهِدْ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>আব্দুল্লাহ ইবনু ’আমর ইবনুল ’আস (রাঃ) বলেন, এক ব্যক্তি আল্লাহর নবীর নিকট এসে বলল, ’আমি আপনার সঙ্গে আল্লাহ তা’আলার কাছে নেকী পাওয়ার উদ্দেশ্যে হিজরত এবং জিহাদের বায়’আত করছি।’ নবী (صلى الله عليه وسلم) বললেন, ’’তোমার পিতা-মাতার মধ্যে কি কেউ জীবিত আছে?’’ সে বলল, ’জী হ্যাঁ; বরং দু’জনই জীবিত রয়েছে।’ রাসূল (صلى الله عليه وسلم) বললেন, ’’তুমি আল্লাহ তা’আলার কাছে নেকী পেতে চাও?’’ সে বলল, ’জী হ্যাঁ।’ তিনি বললেন, ’’তাহলে তুমি তোমার পিতা-মাতার নিকট ফিরে যাও এবং উত্তমরূপে তাদের খিদমত কর।’’ (বুখারী, আর শব্দগুলি মুসলিমের) [১] উভয়ের অন্য এক বর্ণনায় আছে, এক ব্যক্তি তাঁর নিকট এসে জিহাদ করার অনুমতি চাইল। তিনি বললেন, ’’তোমার পিতা-মাতা কি জীবিত আছে?’’ সে বলল, ’জী হ্যাঁ।’ তিনি বললেন, ’’অতএব তুমি তাদের (সেবা করার) মাধ্যমে জিহাদ কর।’’</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>وَعَنه، عَنِ النَّبيِّ صلى الله عليه وسلم، قَالَ: «لَيْسَ الوَاصِلُ بِالمُكَافِئ، وَلكِنَّ الوَاصِلَ الَّذِي إِذَا قَطَعَتْ رَحِمُهُ وَصَلَهَا». رواه البخاري</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>নবী (صلى الله عليه وسلم) বলেন, ’’সেই ব্যক্তি সম্পর্ক বজায়কারী নয়, যে সম্পর্ক বজায় করার বিনিময়ে বজায় করে। বরং প্রকৃত সম্পর্ক বজায়কারী হল সেই ব্যক্তি, যে কেউ তার সাথে সম্পর্ক ছিন্ন করলে সে তা কায়েম করে।’’ (বুখারী) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>وَعَن عَائِشَةَ، قَالَتْ : قَالَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم: «الرَّحِمُ مُعَلَّقَةٌ بِالعَرْشِ تَقُولُ : مَنْ وَصَلَنِي، وَصَلَهُ اللهُ، وَمَنْ قَطَعَنِي، قَطَعَهُ اللهُ». مُتَّفَقٌ عَلَيهِ</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>আয়েশা (রাঃ) বলেন, রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন, ’’জ্ঞাতিবন্ধন আরশে ঝুলন্ত আছে এবং সে বলছে, ’যে আমাকে অবিচ্ছিন্ন রাখবে, আল্লাহ তাঁর সম্পর্ক তার সাথে অবিচ্ছিন্ন রাখবেন। আর যে আমাকে বিচ্ছিন্ন করবে, আল্লাহ তাঁর সম্পর্ক তার সাথে বিচ্ছিন্ন করবেন।’’ (বুখারী, মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>وَعَن أُمِّ الْمُؤمِنِينَ مَيمُونَةَ بِنتِ الحَارِثِ رَضِيَ اللهُ عَنهَا: أنَّهَا أعْتَقَتْ وَلِيدَةً وَلَمْ تَستَأذِنِ النَّبيَّ صلى الله عليه وسلم، فَلَمَّا كَانَ يَوْمُهَا الَّذِي يَدُورُ عَلَيْهَا فِيهِ، قَالَتْ: أشَعَرْتَ يَا رَسُولَ اللهِ صلى الله عليه وسلم، أنِّي أعتَقْتُ وَلِيدَتِي؟ قَالَ: «أَوَ فَعَلْتِ؟» قَالَتْ: نَعَمْ. قَالَ: « أما إنَّكِ لَوْ أعْطَيْتِهَا أخْوَالَكِ كَانَ أعْظَمَ لأََِجْرِكِ». مُتَّفَقٌ عَلَيهِ</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>উম্মুল মু’মেনীন মায়মূনাহ বিনতিল হারেস (রাঃ)া কর্তৃক বর্ণিত, তিনি তাঁর একটি ক্রীতদাসীকে নবী (صلى الله عليه وسلم)-এর অনুমতি না নিয়েই মুক্ত করলেন। অতঃপর যখন ঐ দিন এসে পৌঁছল, যেদিন তাঁর কাছে নবী (صلى الله عليه وسلم)-এর যাওয়ার পালা, তখন মায়মূনাহ বললেন, ’হে আল্লাহর রাসূল! আমি যে আমার ক্রীতদাসীকে মুক্ত করে দিয়েছি, আপনি কি তা বুঝতে পেরেছেন?’ তিনি বললেন, ’’তুমি কি (সত্যই) এ কাজ করেছ?’’ মায়মূনা বললেন, ’জী হ্যাঁ।’ তিনি বললেন, ’’তুমি যদি ক্রীতদাসীটিকে তোমার মামাদেরকে দিতে, তাহলে তুমি বেশী সওয়াব পেতে।’’ (বুখারী ও মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>وَعَن أسماءَ بِنتِ أَبي بَكرٍ الصِّدِّيقِ رَضِيَ اللهُ عَنهُمَا، قَالَتْ : قَدِمَتْ عَلَيَّ أُمِّي وَهِيَ مُشرِكَةٌ في عَهْدِ رسولِ الله صلى الله عليه وسلم، فاسْتَفْتَيْتُ رَسُولَ الله صلى الله عليه وسلم، قُلْتُ : قَدِمَتْ عَلَيَّ أُمِّي وَهِيَ رَاغِبَةٌ، أفَأصِلُ أُمِّي ؟ قَالَ: «نَعَمْ، صِلِي أُمَّكِ». مُتَّفَقٌ عَلَيهِ</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, নবী (صلى الله عليه وسلم)-এর যুগে আমার অমুসলিম মা আমার কাছে এল। আমি নবী (صلى الله عليه وسلم)-কে জিজ্ঞেস করলাম; বললাম, ’আমার মা (ইসলাম) অপছন্দ করা অবস্থায় (আমার সম্পদের লোভ রেখে) আমার নিকট এসেছে, আমি তার সাথে সম্পর্ক বজায় রাখব কি?’ তিনি বললেন, ’’হ্যাঁ, তুমি তোমার মায়ের সাথে সম্পর্ক বজায় রাখ।’’ (বুখারী ও মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>وَعَن زَينَبَ الثَّقَفِيَّةِ امرَأَةِ عَبدِ اللهِ بنِ مَسعُودٍ رَضِيَ اللهُ عَنهُ وَعَنهَا، قَالَتْ : قَالَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم: «تَصَدَّقْنَ يَا مَعْشَرَ النِّسَاءِ وَلَوْ مِنْ حُلِيِّكُنَّ»، قَالَتْ : فَرَجَعْتُ إِلَى عَبدِ اللهِ بنِ مَسعُودٍ، فَقُلتُ لَهُ : إنَّكَ رَجُلٌ خَفِيفُ ذَاتِ اليَدِ، وَإنَّ رَسُولَ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم قَدْ أمَرَنَا بِالصَّدَقَةِ فَأْتِهِ، فَاسأَلهُ، فإنْ كَانَ ذلِكَ يْجُزِئُُ عَنِّي وَإلاَّ صَرَفْتُهَا إِلَى غَيْرِكُمْ . فَقَالَ عَبدُ اللهِ : بَلِ ائْتِيهِ أنتِ، فانْطَلَقتُ، فَإذَا امْرأةٌ مِنَ الأنْصارِ بِبَابِ رسولِ اللهِ صلى الله عليه وسلم حَاجَتي حَاجَتُها، وَكَانَ رَسُولُ الله صلى الله عليه وسلم قَدْ أُلْقِيَتْ عَلَيهِ المَهَابَةُ، فَخَرجَ عَلَيْنَا بِلاَلٌ، فَقُلْنَا لَهُ : ائْتِ رَسُولَ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم، فَأخْبِرْهُ أنَّ امْرَأتَيْنِ بِالبَابِ تَسألانِكَ : أُتُجْزِئُ الصَّدَقَةُ عَنْهُمَا عَلَى أزْواجِهمَا وَعَلَى أيْتَامٍ في حُجُورِهِما ؟، وَلاَ تُخْبِرْهُ مَنْ نَحْنُ، فَدَخلَ بِلاَلٌ عَلَى رَسُولِ الله صلى الله عليه وسلم، فَسَأَلَهُ، فَقَالَ لَهُ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم: «مَنْ هُمَا ؟»قَالَ : امْرَأةٌ مِنَ الأنْصَارِ وَزَيْنَبُ . فَقَالَ رَسُولُ الله صلى الله عليه وسلم: «أيُّ الزَّيَانِبِ هِيَ ؟»، قَالَ: امْرَأةُ عَبدِ الله، فَقَالَ رَسُولُ الله صلى الله عليه وسلم: «لَهُمَا أجْرَانِ : أجْرُ القَرَابَةِ وَأجْرُ الصَّدَقَةِ». مُتَّفَقٌ عَلَيهِ</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>আব্দুল্লাহ ইবনু মাসঊদ (রাঃ)-এর স্ত্রী যায়নাব (রাঃ)া কর্তৃক বর্ণিত, তিনি বলেন, একদা রাসূলুল্লাহ (صلى الله عليه وسلم) বললেন, ’’হে মহিলাগণ! তোমরা সাদকাহ কর; যদিও তোমাদের অলংকার থেকে হয়।’’ যায়নাব (রাঃ)া বলেন, সুতরাং আমি (আমার স্বামী) আব্দুল্লাহ ইবনু মাসঊদ (রাঃ)-এর নিকট এসে বললাম, ’আপনি গরীব মানুষ, আর রাসূলুল্লাহ (صلى الله عليه وسلم) আমাদেরকে সাদকাহ করার নির্দেশ দিয়েছেন। অতএব আপনি তাঁর নিকট গিয়ে এ কথা জেনে আসুন যে, (আমি যে, আপনার উপর ও আমার তত্ত্বাবধানে প্রতিপালিত এতীমদের উপর খরচ করি তা) আমার পক্ষ থেকে সাদকাহ হিসাবে যথেষ্ট হবে কি? নাকি আপনাদেরকে বাদ দিয়ে আমি অন্যকে দান করব?’ ইবনু মাসঊদ (রাঃ) বললেন, ’বরং তুমিই রাসূলুল্লাহ (صلى الله عليه وسلم)-এর কাছে জেনে এসো।’ সুতরাং আমি তাঁর নিকট গেলাম। দেখলাম, তাঁর দরজায় আরও একজন আনসারী মহিলা দাঁড়িয়ে আছে, তার প্রয়োজনও আমার প্রয়োজনের অনুরূপ। আল্লাহর রাসূল (صلى الله عليه وسلم)-কে ভাবগম্ভীরতা দান করা হয়েছিল। (তাঁকে সকলেই ভয় করত।) ইতোমধ্যে বিলাল (রাঃ)-কে আমাদের পাশ দিয়ে যেতে দেখে বললাম, আপনি রাসূলুল্লাহ (صلى الله عليه وسلم)-এর কাছে গিয়ে বলুন, ’দরজার কাছে দু’জন মহিলা আপনাকে জিজ্ঞাসা করছে যে, তারা যদি নিজ স্বামী ও তাদের তত্ত্বাবধানে প্রতিপালিত এতীমদের উপর খরচ করে, তাহলে তা সাদকাহ হিসাবে যথেষ্ট হবে কি? আর আমরা কে, সে কথা জানাবেন না।’ তিনি প্রবেশ করে তাঁকে জিজ্ঞেস করলেন। রাসূলুল্লাহ (صلى الله عليه وسلم) বললেন, ’’তারা কে?’’ বিলাল (রাঃ) বললেন, ’এক আনসারী মহিলা ও যায়নাব।’ তিনি আবার জিজ্ঞেস করলেন, ’’কোন্ যায়নাব?’’ বিলাল (রাঃ) উত্তর দিলেন, ’আব্দুল্লাহর স্ত্রী।’ রাসূলুল্লাহ (صلى الله عليه وسلم) বললেন, ’’তাদের জন্য দু’টি সওয়াব রয়েছে, আত্মীয়তার বন্ধন বজায় রাখার সওয়াব এবং সাদকাহ করার সওয়াব।’’ (বুখারী-মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>وَعَن أَبي سُفيَانَ صَخرِ بنِ حَربٍ رضي الله عنه في حَديثِهِ الطويل في قِصَّةِ هِرَقْلَ: أنَّ هِرَقْلَ قَالَ لأَبِي سُفْيَانَ: فَمَاذَا يَأمُرُكُمْ بِهِ؟ يَعْنِي النَّبيّ صلى الله عليه وسلم، قَالَ: قُلْتُ: يَقُولُ: « اعْبُدُوا اللهَ وَحْدَهُ، وَلاَ تُشْرِكُوا بِهِ شَيئاً، واتْرُكُوا مَا يَقُولُ آبَاؤُكُمْ، وَيَأمُرُنَا بِالصَّلاةِ، وَالصِّدْقِ، والعَفَافِ، والصِّلَةِ»مُتَّفَقٌ عَلَيهِ</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>আবূ সুফিয়ান সাখর ইবনু হারব (রাঃ) থেকে (রোম-সম্রাট) হিরাক্লিয়াসের ঘটনা সম্পর্কিত দীর্ঘ হাদীসে বর্ণিত, হিরাক্লিয়াস আবূ সুফিয়ানকে বললেন, ’তিনি (নবী (صلى الله عليه وسلم)) তোমাদেরকে কী নির্দেশ দেন?’ আবূ সুফিয়ান বলেন, আমি বললাম, ’তিনি বলেন, ’’তোমরা এক আল্লাহর ইবাদত কর এবং তার সাথে কোন কিছুকে অংশীদার করো না এবং তোমাদের বাপ-দাদার ভ্রান্ত পথ পরিত্যাগ কর।’’ আর তিনি আমাদেরকে নামায পড়ার, সত্যবাদিতার, চারিত্রিক পবিত্রতার এবং আত্মীয়তা বজায় রাখার আদেশ দেন।’ (বুখারী ও মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>وَعَن أَبي ذَرٍّ رضي الله عنه، قَالَ : قَالَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم: «إنَّكُمْ سَتَفْتَحُونَ أرْضاً يُذْكَرُ فِيهَا القِيرَاطُ» . وفي رِوَايَةٍ: «سَتَفْتَحُونَ مِصْرَ وَهِيَ أرْضٌ يُسَمَّى فِيهَا القِيراطُ، فَاسْتَوْصُوا بأهْلِهَا خَيْراً ؛ فَإنَّ لَهُمْ ذِمَّةً وَرَحِماً»وفي رواية: «فَإِذَا افتَتَحتُمُوهَا، فَأَحسِنُوا إِلَى أَهلِهَا ؛ فَإِنَّ لَهُم ذِمَّةً وَرَحِماً»، أَوْ قَالَ: «ذِمَّةً وصِهْراً». رواه مسلم</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন, ’’তোমরা অদূর ভবিষ্যতে এমন এক এলাকা জয় করবে, যেখানে ক্বীরাত্ব (এক দ্বীনারের ২০ ভাগের একভাগ স্বর্ণমুদ্রা) উল্লেখ করা হয়।’’ অন্য এক বর্ণনায় আছে, ’’তোমরা অচিরে মিসর জয় করবে এবং এটা এমন ভূখণ্ড যেখানে কীরাত্ব (শব্দ) সচরাচর বলা হয়। (সেখানে ঐ মুদ্রা প্রচলিত।) তোমরা তার অধিবাসীদের সাথে ভাল ব্যবহার করো। কেননা, তাদের প্রতি (আমাদের) দায়িত্ব (অধিকার ও মর্যাদা) এবং আত্মীয়তা রয়েছে।’’ অন্য এক বর্ণনায় আছে, ’’সুতরাং যখন তোমরা তা জয় করবে, তখন তার অধিবাসীর প্রতি সদ্ব্যবহার করো। কেননা, তাদের প্রতি (আমাদের) দায়িত্ব (অধিকার ও মর্যাদা) এবং আত্মীয়তা রয়েছে।’’ অথবা বললেন, ’’দায়িত্ব (অধিকার ও মর্যাদা) এবং বৈবাহিক সম্পর্ক রয়েছে।’’ (মুসলিম)[১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>وَعَن أَبي هُرَيرَةَ رضي الله عنه، قَالَ : لَمَّا نَزَلَت هَذِهِ الآيَةُ : ﴿ وَأَنذِرۡ عَشِيرَتَكَ ٱلۡأَقۡرَبِينَ ٢١٤ ﴾ [الشعراء: ٢١٤] دَعَا رَسُولُ الله صلى الله عليه وسلم قُرَيْشاً، فَاجْتَمَعُوا فَعَمَّ وَخَصَّ، وَقالَ: «يَا بَنِي عَبْدِ شَمْسٍ، يا بَنِي كَعْبِ بْنِ لُؤَيٍّ، أنقِذُوا أنْفُسَكُمْ مِنَ النَّارِ، يَا بَنِي مُرَّةَ بنِ كَعْبٍ، أنْقِذُوا أنْفُسَكُمْ مِنَ النَّارِ، يَا بَنِي عَبْدِ مَنَاف، أنْقِذُوا أنْفُسَكُمْ مِنَ النَّارِ، يَا بَنِي هَاشِم، أَنقِذُوا أَنفُسَكُم مِنَ النَّار، يَا بَني عَبدِ الْمُطَّلِب، أَنقِذُوا أَنفُسَكُم مِنَ النَّار، يَا فَاطِمَةُ، أنْقِذِي نَفْسَكِ مِنَ النَّارِ . فَإنِّي لاَ أمْلِكُ لَكُمْ مِنَ اللهِ شَيئاً، غَيْرَ أنَّ لَكُمْ رَحِماً سَأبُلُّهَا بِبِلالِهَا». رواه مسلم</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>যখন এ আয়াত অবতীর্ণ হল যার অর্থ হল, ’’তুমি তোমার নিকট আত্মীয়বর্গকে সতর্ক কর।’’ (সূরা শুআরা ২১৪ আয়াত) তখন রাসূলুল্লাহ (صلى الله عليه وسلم) কুরায়েশ (সম্প্রদায়)কে আহ্বান করলেন। সুতরাং তারা একত্রিত হল। অতঃপর তিনি সাধারণ ও বিশেষভাবে (সম্বোধন করে) বললেন, ’’হে বানী আব্দে শাম্‌স! হে বানী কা’ব ইবনুলুআই! তোমরা নিজেদেরকে জাহান্নাম থেকে বাঁচাও। হে বানী মুর্রাহ ইবনু কা’ব! তোমরা নিজেদেরকে জাহান্নাম থেকে বাঁচাও। হে বানী আব্দে মানাফ! তোমরা নিজেদেরকে জাহান্নাম থেকে বাঁচাও। হে বানী হাশেম! তোমরা নিজেদেরকে জাহান্নাম থেকে বাঁচাও। হে বানী আব্দিল মুত্তালিব! তোমরা নিজেদেরকে জাহান্নাম থেকে বাঁচাও। হে ফাতেমা! তুমি নিজেকে জাহান্নাম থেকে বাঁচাও। কারণ, আমি আল্লাহর নিকট তোমাদের (উপকার-অপকার) কিছুরই মালিক নই।তবে তোমাদের সাথে (আমার) যে আত্মীয়তা রয়েছে তা আমি (দুনিয়াতে) অবশ্যই আর্দ্র রাখব।(আখেরাতে আমার আনুগত্য ছাড়া আত্মীয়তা কোনো কাজে আসবে না।)’’ (মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>وَعَن أَبي عَبدِ اللهِ عَمرِو بنِ العَاصِ رَضِيَ اللهُ عَنهُمَا، قَالَ : سَمِعتُ رَسُولَ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم جِهَاراً غَيْرَ سِرٍّ، يَقُولُ: «إنَّ آل بَني فُلاَنٍ لَيْسُوا بِأولِيَائِي، إِنَّمَا وَلِيِّيَ اللهُ وَصَالِحُ المُؤْمِنينَ، وَلَكِنْ لَهُمْ رَحِمٌ أبُلُّهَا بِبلاَلِهَا». مُتَّفَقٌ عَلَيهِ، واللفظ للبخاري</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>আবূ আব্দুল্লাহ ’আমর ইবনু ’আস (রাঃ) বলেন, আমি রাসূলুল্লাহ (صلى الله عليه وسلم)-কে গোপনে নয় প্রকাশ্যে বলতে শুনেছি, তিনি বলেছেন, ’’অমুক গোত্রের লোকেরা (যারা আমার প্রতি ঈমান আনেনি তারা) আমার বন্ধু নয়। আমার বন্ধু তো আল্লাহ এবং নেক মু’মিনগণ। কিন্তু ওদের সাথে আমার রক্তের সম্পর্ক রয়েছে,আমি (দুনিয়াতে) অবশ্যই তা আর্দ্র রাখব।’’ (বুখারী ও মুসলিম, শব্দ বুখারীর) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>وَعَن أَبي أَيُّوبٍ خَالِدِ بنِ زَيدٍ الأَنصَارِي رضي الله عنه : أنَّ رَجُلاً قَالَ : يَا رَسُولَ اللهِ صلى الله عليه وسلم، أخْبِرْني بِعَمَلٍ يُدْخِلُني الجَنَّةَ، وَيُبَاعِدُني مِنَ النَّارِ . فَقَالَ النَّبيُّ صلى الله عليه وسلم: «تَعْبُدُ الله، وَلاَ تُشْرِكُ بِهِ شَيئاً، وَتُقِيمُ الصَّلاةَ، وتُؤتِي الزَّكَاةَ، وتَصِلُ الرَّحمَ». مُتَّفَقٌ عَلَيهِ</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>আবূ আইয়ূব খালেদ ইবনু যায়েদ আনসারী (রাঃ) কর্তৃক বর্ণিত, এক ব্যক্তি বলল, ’হে আল্লাহর রাসূল! আপনি আমাকে এমন আমল বলে দিন, যা আমাকে জান্নাতে নিয়ে যাবে এবং জাহান্নাম থেকে দূরে রাখবে।’ নবী (صلى الله عليه وسلم) বললেন, ’’তুমি আল্লাহর ইবাদত করবে, তার সাথে কাউকে অংশীদার করবে না, নামায প্রতিষ্ঠা করবে, যাকাত দেবে এবং রক্ত সম্পর্ক বজায় রাখবে।’’ (বুখারী ও মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>وَعَن سَلمَانَ بنِ عَامِرٍ رضي الله عنه، عَنِ النَّبيِّ صلى الله عليه وسلم، قَالَ » إِذا أَفْطَرَ أَحَدُآُمْ فَلْيُفْطِرْعَلَى تَمرٍ ، فَإِنَّهُ برآَةٌ ، فَإِنْ لَمْ يجِد تَمْراً ، فَالماءُ ، فَإِنَّهُ طُهُورٌ « وقال: » الصَّدَقَةُ عَلَى المِسكينِ صَدَقةٌ، وعَلَى ذِي الرَّحِمِ ثِنْتَانِ : صَدَقَةٌ وَصِلَةٌ». رواه الترمذي، وَقالَ: حديث حسن».</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>নবী (صلى الله عليه وسلم) বলেন, তোমাদের কেউ যখন ইফতার করে, সে যেন খেজুর দিয়ে ইফতার করে, কেননা এতে বরকত রয়েছে। আর যদি সে খেজুর না পায়, তাহলে সে যেন পানি দিয়ে ইফতার করে, কেননা এটি পবিত্র। [- হাদিসের এই অংশটুকু সহিহ নয়]তিনি আরো বলেন "মিসকীনকে সাদকাহ করলে সাদকাহ (করার সওয়াব) হয়। আর আত্মীয়কে সাদকাহ করলে দু’টি সওয়াব হয়ঃ সাদকাহ করার ও আত্মীয়তার বন্ধন বজায় রাখার।’’ (তিরমিযী এটিকে হাসান বলেছেন [১])</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>وَعَنِ ابنِ عُمَرَ رَضِيَ اللهُ عَنهُمَا، قَالَ: كَانَتْ تَحْتِي امْرَأةٌ، وَكُنْتُ أحِبُّهَا، وَكَانَ عُمَرُ يَكْرَهُهَا، فَقَالَ لي : طَلِّقْهَا، فَأبَيْتُ، فَأتَى عُمَرُ رضي الله عنه النَّبيَّ صلى الله عليه وسلم، فَذَكَرَ ذلِكَ لَهُ، فَقَالَ النَّبيّ صلى الله عليه وسلم: «طَلِّقْهَا». رواه أَبُو داود والترمذي، وَقالَ: حديث حسن صحيح»</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ইবনু উমার (রাঃ) বলেন, ’আমার বিবাহ বন্ধনে এক স্ত্রী ছিল, যাকে আমি ভালবাসতাম। কিন্তু (আমার পিতা) উমর তাকে অপছন্দ করতেন। সুতরাং তিনি আমাকে বললেন, ’’তুমি ওকে ত্বালাক দাও।’’ কিন্তু আমি (তা) অস্বীকার করলাম। অতঃপর উমর (রাঃ) নবী (صلى الله عليه وسلم)-এর নিকট এলেন এবং এ কথা উল্লেখ করলেন। নবী (صلى الله عليه وسلم) (আমাকে) বললেন, ’’তুমি ওকে ত্বালাক দিয়ে দাও।’’ (সুতরাং আমি তাকে ত্বালাক দিয়ে দিলাম।) (আবূ দাঊদ, তিরমিযী, হাসান সহীহ সূত্রে) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>وَعَن أَبي الدَّردَاءِ رضي الله عنه: أَنَّ رَجُلاً أَتَاهُ، قَالَ : إنّ لِي امرَأةً وإنّ أُمِّي تَأمُرُنِي بِطَلاقِهَا، فَقَالَ : سَمِعْتُ رَسُولَ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم، يَقُولُ: «الوَالِدُ أوْسَطُ أبْوَابِ الجَنَّةِ، فَإنْ شِئْتَ، فَأضِعْ ذلِكَ البَابَ، أَو احْفَظْهُ». رواه الترمذي، وَقالَ: حديث حسن صحيح»</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>এক ব্যক্তি তাঁর নিকট এসে বলল, ’আমার এক স্ত্রী আছে। আমার মা তাকে ত্বালাক দেওয়ার নির্দেশ দিচ্ছেন।’ আবূ দারদা বললেন, আমি রাসূলুল্লাহ (صلى الله عليه وسلم)-কে বলতে শুনেছি, ’’পিতা-মাতা জান্নাতের দুয়ারসমূহের মধ্যে সর্বশ্রেষ্ঠ দুয়ার। সুতরাং তুমি যদি চাও, তাহলে এ দুয়ারকে নষ্ট কর অথবা তার রক্ষণাবেক্ষণ কর।’’ (তিরমিযী, হাসান সহীহ সূত্রে)[১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>وَعَنِ البَرَاءِ بنِ عَازِبٍ رَضِيَ اللهُ عَنهُمَا، عَنِ النَّبيِّ صلى الله عليه وسلم، قَالَ: «الخَالةُ بِمَنْزِلَةِ الأُمِّ». رواه الترمذي، وَقالَ: حديث حسن صحيح»</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>বারা ইবনু ’আযেব (রাঃ) কৃর্তক বর্ণিত, নবী (صلى الله عليه وسلم) বলেন, ’’খালা মায়ের মর্যাদায় অধিষ্ঠিত।’’ (তিরমিযী)[১] এ প্রসঙ্গে আরো অনেক সহীহ ও প্রসিদ্ধ হাদীস রয়েছে, তার মধ্যে গুহাবন্দী তিন ব্যক্তির (১৩নং) হাদীস, জুরাইজের (২৬৪নং) লম্বা হাদীস এবং আরো অন্যান্য সহীহ ও প্রসিদ্ধ হাদীস সংক্ষেপ করার উদ্দেশ্যে উল্লেখ করলাম না। তার মধ্যে ’আমর ইবনু আবাসাহর (৪৪৩নং) হাদীসটি বড়ই গুরুত্বপূর্ণ, যাতে ইসলামের অনেকানেক মৌলনীতি ও শিষ্টাচারিতার কথা বর্ণিত হয়েছে। যেটিকে পূর্ণরূপে ’আল্লাহর দয়ার আশা রাখার গুরুত্ব’ পরিচ্ছেদে উল্লেখ করব -ইনশাআল্লাহ। যে হাদীসে সাহাবী (রাঃ) বলেন, আমি নবুঅতের শুরুর দিকে মক্কায় নবী (صلى الله عليه وسلم)-এর নিকটে এলাম এবং বললাম, ’আপনি কি?’ তিনি বললেন, ’’আমি নবী।’’ আমি বললাম, ’নবী কি?’ তিনি বললেন, ’’আমাকে মহান আল্লাহ প্রেরণ করেছেন।’’ আমি বললাম, ’ কী নির্দেশ দিয়ে প্রেরণ করেছেন?’ তিনি বললেন, ’’জ্ঞাতিবন্ধন অক্ষুণ্ণ রাখা, মূর্তি ভেঙ্গে ফেলা, আল্লাহকে একক উপাস্য মানা এবং তাঁর সাথে কাউকে শরীক না করার নির্দেশ দিয়ে।---’’ (অতঃপর পূর্ণ হাদীস বর্ণনা করেছেন। আর আল্লাহই অধিক জানেন।)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>وَعَنْ سَعدِ بنِ أَبِي وَقَّاصٍ رضي الله عنه، قَالَ: عَادَنِي رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم، فَقَالَ: « اَللهم اشْفِ سَعْداً، اَللهم اشْفِ سَعْداً، اَللهم اشْفِ سَعْداً ». رواه مسلم</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>সা’দ ইবনে আবী অক্কাস (রাঃ) বলেন, রাসূলুল্লাহ (صلى الله عليه وسلم) (আমার অসুস্থ অবস্থায়) আমাকে দেখা করতে এসে বললেন, ’’হে আল্লাহ! সা’দকে রোগমুক্ত কর, হে আল্লাহ! সা’দকে রোগমুক্ত কর। হে আল্লাহ! সা’দকে রোগমুক্ত কর।’’ (মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>967</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>وَعَنْ أَبي سَعِيدٍ وأَبِي هُرَيرَةَ رَضِيَ اللهُ تَعَالَى عَنهُمَا، قَالاَ: قَالَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم: إِذَا خَرَجَ ثَلاَثَةٌ في سَفَرٍ فَليُؤَمِّرُوا أحَدَهُمْ . حديث حسن، رواه أَبُو داود بإسنادٍ حسن</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>আবূ সা’ঈদ ও আবূ হুরাইরা (রাদ্বিয়াল্লাহু তা’আলা আনহুমা) বলেন, রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন, ’’যখন তিন ব্যক্তি সফরে বের হবে, তখন তারা যেন তাদের একজনকে আমীর বানিয়ে নেয়।’’ (আবূ দাঊদ হাসান সূত্রে)[১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>عَنْ أَبِي هُرَيرَةَ رضي الله عنه، قَالَ: قَالَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم: إِذَا سَافَرْتُمْ فِي الخِصْبِ، فَأَعْطُوا الإبلَ حَظَّهَا مِنَ الأَرْضِ، وَإِذَا سَافَرْتُمْ فِي الجَدْبِ، فَأَسْرِعُوا عَلَيْهَا السَّيْرَ، وَبَادِرُوا بِهَا نِقْيَهَا، وَإِذَا عَرَّسْتُمْ، فَاجْتَنِبُوا الطَّرِيقَ ؛ فَإنَّهَا طُرُقُ الدَّوَابِّ، وَمَأوَى الهَوَامِّ بِاللَّيْلِ . رواه مسلم</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন, ’’যখন তোমরা সবুজ-শ্যামল ঘাসে ভরা যমীনে সফর করবে, তখন উটকে তার যমীনের অংশ দাও (অর্থাৎ কিছুক্ষণ চরতে দাও)। আর যখন তোমরা ঘাস-পানিবিহীন যমীনে সফর করবে, তখন তার উপর চড়ে দ্রুত চলো এবং তার শক্তি শেষ হওয়ার পূর্বেই গন্তব্যস্থানে পৌঁছে যাও। আর যখন তোমরা রাতে বিশ্রামের জন্য কোন স্থানে অবতরণ করবে, তখন আম রাস্তা থেকে দূরে থাকো। কারণ, তা রাতে (হিংস্র) জন্তুদের রাস্তা এবং (বিষাক্ত) পোকামাকড়ের আশ্রয় স্থল।’’(মুসলিম)[১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>وَعَنْ أَبي ثَعْلَبَةَ الخُشَنِيِّ رضي الله عنه، قَالَ: كَانَ النَّاسُ إِذَا نَزَلُوا مَنْزِلاً تَفَرَّقُوا فِي الشِّعَابِ وَالأوْدِيَةِ . فَقَالَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم: إنَّ تَفَرُّقَكُمْ فِي هَذِهِ الشِّعَابِ وَالأَوْدِيَةِ إِنَّمَا ذَلِكُمْ مِنَ الشَّيْطَانِ! فَلَمْ يَنْزِلُوا بَعْدَ ذَلِكَ مَنْزِلاً إِلاَّ انْضَمَّ بَعْضُهُمْ إِلَى بَعْضٍ. رواه أَبُو داود بإسناد حسن</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>আবূ সা’লাবা খুশানী (রাঃ) বলেন, লোকেরা যখন কোন স্থানে অবতরণ করতেন, তখন তাঁরা গিরিপথ ও উপত্যকায় ছড়িয়ে যেতেন। রাসূলুল্লাহ (صلى الله عليه وسلم) বললেন, ’’তোমাদের এ সকল গিরিপথে ও উপত্যকায় বিক্ষিপ্ত হওয়া শয়তানের কাজ।’’ এরপর তাঁরা যখনই কোন মঞ্জিলে অবতরণ করতেন, তখন একে অপরের সাথে মিলিত হয়ে থাকতেন। (আবূ দাউদ) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1222</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>وَعَن أَبِي هُرَيرَةَ رضي الله عنه، قَالَ: قَالَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم «مَا مِنْ صَاحِبِ ذَهَبٍ، وَلاَ فِضَّةٍ، لاَ يُؤَدِّي مِنْهَا حَقَّهَا إِلاَّ إِذَا كَانَ يَومُ القِيَامَةِ صُفِّحَتْ لَهُ صَفَائِحُ مِنْ نَارٍ، فَأُحْمِيَ عَلَيْهَا في نَارِ جَهَنَّمَ، فَيُكْوَى بِهَا جَنْبُهُ، وَجَبِينُهُ، وَظَهْرُهُ، كُلَّمَا بَرَدَتْ أُعِيدَتْ لَهُ في يَومٍ كَانَ مِقْدَارُهُ خَمْسِينَ ألْفَ سَنَةٍ، حَتَّى يُقْضَى بَيْنَ العِبَادِ فَيَرَى سَبيلَهُ، إِمَّا إِلَى الجَنَّةِ، وَإِمَّا إِلَى النَّارِ» قِيلَ: يَا رَسُولَ اللهِ صلى الله عليه وسلم، فَالإِبِلُ ؟ قَالَ: «وَلاَ صَاحِبِ إِبِلٍ لاَ يُؤَدِّي مِنْهَا حَقَّهَا، وَمِنْ حَقِّهَا حَلْبُهَا يَومَ وِرْدِهَا، إِلاَّ إِذَا كَانَ يَومُ القِيَامَةِ بُطِحَ لَهَا بِقَاعٍ قَرْقَرٍ أَوْفَرَ مَا كَانَتْ، لاَ يَفْقِدُ مِنْهَا فَصِيلاً وَاحِداً، تَطَؤُهُ بِأَخْفَافِهَا، وَتَعَضُّهُ بِأفْوَاهِهَا، كُلَّمَا مَرَّ عَلَيْهِ أُولاَهَا، رُدَّ عَلَيْهِ أُخْرَاهَا فِي يَوْمٍ كَانَ مِقْدَارُهُ خَمْسِينَ ألْفَ سَنَةٍ، حَتَّى يُقْضى بَيْنَ العِبَادِ، فَيَرَى سَبِيلَهُ، إمَّا إِلَى الجَنَّةِ، وَإِمَّا إِلَى النَّارِ». قِيلَ: يَا رَسُولَ اللهِ صلى الله عليه وسلم، فَالبَقَرُ وَالغَنَمُ ؟ قَالَ: «وَلاَ صَاحِبِ بَقَرٍ وَلاَ غَنَمٍ لاَ يُؤَدِّي مِنْهَا حَقَّهَا، إِلاَّ إِذَا كَانَ يَوْمُ القِيَامَةِ، بُطِحَ لَهَا بقَاعٍ قَرْقَرٍ، لاَ يَفْقِدُ مِنْهَا شَيْئاً، لَيْسَ فِيهَا عَقْصَاءُ، وَلاَ جَلْحَاءُ، وَلاَ عَضْبَاءُ، تَنْطَحُهُ بقُرُونِهَا، وَتَطَؤُهُ بِأَظْلاَفِهَا، كُلَّمَا مرَّ عَلَيْهِ أُولاَهَا، رُدَّ عَلَيْهِ أُخْرَاهَا، فِي يَومٍ كَانَ مِقْدَارُهُ خَمْسِينَ ألْفَ سَنَة حَتَّى يُقْضَى بَيْنَ العِبَادِ، فَيَرَى سَبيِلَهُ، إِمَّا إِلَى الجَنَّةِ، وَإِمَّا إِلَى النَّارِ». قِيلَ: يَا رَسُولَ اللهِ صلى الله عليه وسلم فَالخَيْلُ ؟ قَالَ: «الخَيلُ ثَلاَثَةٌ: هِيَ لِرَجُلٍ وِزْرٌ، وَهِيَ لِرَجُلٍ سِتْرٌ، وَهِيَ لِرَجُلٍ أَجْرٌ . فَأَمَّا الَّتِي هِيَ لَهُ وِزْرٌ فَرَجُلٌ رَبَطَهَا رِيَاءً وَفَخْراً وَنِوَاءً عَلَى أَهْلِ الإِسْلاَمِ، فَهِيَ لَهُ وِزْرٌ، وَأَمَّا الَّتِي هِيَ لَهُ سِتْرٌ، فَرَجُلٌ رَبَطَهَا فِي سَبيلِ اللهِ، ثُمَّ لَمْ يَنْسَ حَقَّ اللهِ فِي ظُهُورِهَا، وَلاَ رِقَابِهَا، فَهِيَ لَهُ سِتْرٌ، وَأمَّا الَّتِي هِيَ لَهُ أَجْرٌ، فَرَجُلٌ رَبَطَهَا فِي سَبيلِ اللهِ لأَهْلِ الإِسْلاَمِ فِي مَرْجٍ، أَوْ رَوْضَةٍ فَمَا أكَلَتْ مِنْ ذَلِكَ المَرْجِ أَوْ الرَّوْضَةِ مِنْ شَيْءٍ إِلاَّ كُتِبَ لَهُ عَدَدَ مَا أَكَلَتْ حَسَنَات وكُتِبَ لَهُ عَدَدَ أَرْوَاثِهَا وَأَبْوَالِهَا حَسَنَات، وَلاَ تَقْطَعُ طِوَلَهَا فَاسْتَنَّتْ شَرَفاً أَوْ شَرَفَيْنِ إِلاَّ كَتَبَ اللهُ لَهُ عَدَدَ آثَارِهَا، وَأَرْوَاثِهَا حَسَنَاتٍ، وَلاَ مَرَّ بِهَا صَاحِبُهَا عَلَى نَهْرٍ، فَشَرِبَتْ مِنْهُ، وَلاَ يُرِيدُ أَنْ يَسْقِيهَا إِلاَّ كَتَبَ اللهُ لَهُ عَدَدَ مَا شَرِبَتْ حَسَنَاتٍ». قِيلَ: يَا رَسُولَ اللهِ صلى الله عليه وسلم فَالْحُمُرُ ؟ قَالَ: «مَا أُنْزِلَ عَلَيَّ في الحُمُرِ شَيْءٌ إِلاَّ هَذِهِ الآيَةُ الفَاذَّةُ الجَامِعَةُ: ( فَمَنْ يَعْمَلْ مِثْقَالَ ذَرَّةٍ خَيْراً يَرَهُ وَمَنْ يَعْمَلْ مِثْقَالَ ذَرَّةٍ شَرّاً يَرَهُ )». متفقٌ عَلَيْهِ، وهذا لفظ مسلم</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন, “প্রত্যেক সোনা ও চাঁদির অধিকারী ব্যক্তি যে তার হক (যাকাত) আদায় করে না, যখন কিয়ামতের দিন আসবে, তখন তার জন্য ঐ সমুদয় সোনা-চাঁদিকে আগুনে দিয়ে বহু পাত তৈরি করা হবে। অতঃপর সেগুলোকে জাহান্নামের আগুনে উত্তপ্ত করা হবে এবং তার দ্বারা তার পাঁজর, কপাল ও পিঠে দাগা হবে। যখনই সে পাত ঠাণ্ডা হয়ে যাবে, তখনই তা পুনরায় গরম করে অনুরূপ দাগার শাস্তি সেই দিনে চলতেই থাকবে, যার পরিমাণ হবে ৫০ হাজার বছরের সমান; যতক্ষণ পর্যন্ত না বান্দাদের মাঝে বিচার-নিষ্পত্তি শেষ করা হয়েছে। অতঃপর সে তার পথ দেখতে পাবে; হয় জান্নাতের দিকে, না হয় জাহান্নামের দিকে।” জিজ্ঞাসা করা হল, ’হে আল্লাহর রাসূল! আর উটের ব্যাপারে কি হবে?’ তিনি বললেন, “প্রত্যেক উটের মালিকও; যে তার হক (যাকাত) আদায় করবে না---আর তার অন্যতম হক এই যে, পানি পান করাবার দিন তাকে দোহন করা (এবং সে দুধ লোকদের দান করা)- যখন কিয়ামতের দিন আসবে, তখন তাকে এক সমতল প্রশস্ত প্রান্তরে উপুড় করে ফেলা হবে। আর তার উট সকল পূর্ণ সংখ্যায় উপস্থিত হবে; ওদের মধ্যে একটি বাচ্চাকেও অনুপস্থিত দেখবে না। অতঃপর সেই উটদল তাদের খুর দ্বারা তাকে দলবে এবং মুখ দ্বারা তাকে কামড়াতে থাকবে। এইভাবে যখনই তাদের শেষ দল তাকে দলে অতিক্রম করে যাবে, তখনই পুনরায় প্রথম দলটি উপস্থিত হবে। তার এই শাস্তি সেদিন হবে, যার পরিমাণ হবে ৫০ হাজার বছরের সমান; যতক্ষণ পর্যন্ত না বান্দাদের মাঝে বিচার-নিষ্পত্তি শেষ করা হয়েছে। অতঃপর সে তার শেষ পরিণাম দর্শন করবে; জান্নাতের অথবা জাহান্নামের।” জিজ্ঞাসা করা হল, ’হে আল্লাহর রাসূল! গরু-ছাগলের ব্যাপারে কি হবে?’ তিনি বললেন, “আর প্রত্যেক গরু-ছাগলের মালিককেও; যে তার হক আদায় করবে না, যখন কিয়ামতের দিন উপস্থিত হবে, তখন তাদের সামনে তাকে এক সমতল প্রশস্ত ময়দানে উপুড় করে ফেলা হবে; যাদের একটিকেও সে অনুপস্থিত দেখবে না এবং তাদের কেউই শিং-বাঁকা, শিং-বিহীন ও শিং-ভাঙ্গা থাকবে না। প্রত্যেকেই তার শিং দ্বারা তাকে আঘাত করতে থাকবে এবং খুর দ্বারা দলতে থাকবে। তাদের শেষ দলটি যখনই (ঢুস মেরে ও দলে) পার হয়ে যাবে তখনই প্রথম দলটি পুনরায় এসে উপস্থিত হবে। এই শাস্তি সেদিন হবে যার পরিমাণ ৫০ হাজার বছরের সমান; যতক্ষণ পর্যন্ত না বান্দাদের মাঝে বিচার-নিষ্পত্তি শেষ করা হয়েছে। অতঃপর সে তার রাস্তা ধরবে; জান্নাতের দিকে, নতুবা জাহান্নামের দিকে।” জিজ্ঞাসা করা হল, ’হে আল্লাহর রাসূল! আর ঘোড়া সম্পর্কে কি হবে?’ তিনি বললেন, “ঘোড়া হল তিন প্রকারের; ঘোড়া কারো পক্ষে পাপের বোঝা, কারো পক্ষে পর্দাস্বরূপ এবং কারো জন্য সওয়াবের বিষয়। যে ঘোড়া তার মালিকের পক্ষে পাপের বোঝা তা হল সেই ব্যক্তির ঘোড়া, যে লোক প্রদর্শন, গর্বপ্রকাশ এবং মুসলিমদের প্রতি শত্রুতার উদ্দেশ্যে পালন করেছে। এ ঘোড়া হল তার মালিকের জন্য পাপের বোঝা। যে ঘোড়া তার মালিকের পক্ষে পর্দাস্বরূপ, তা হল সেই ব্যক্তির ঘোড়া, যাকে সে আল্লাহর রাস্তায় (জিহাদের জন্য) প্রস্তুত রেখেছে। অতঃপর সে তার পিঠ ও গর্দানে আল্লাহর হক ভুলে যায়নি। তার যথার্থ প্রতিপালন করে জিহাদ করেছে। এ ঘোড়া হল তার মালিকের পক্ষে (জাহান্নাম হতে অথবা ইজ্জত-সম্মানের জন্য) পর্দাস্বরূপ। আর যে ঘোড়া তার মালিকের জন্য সওয়াবের বিষয়, তা হল সেই ঘোড়া যাকে তার মালিক মুসলিমদের (প্রতিরক্ষার) উদ্দেশ্যে কোন চারণভূমি বা বাগানে প্রস্তুত রেখেছে। তখন সে ঘোড়া ঐ চারণভূমি বা বাগানের যা কিছু খাবে, তার খাওয়া ঐ (ঘাস-পাতা) পরিমাণ সওয়াব মালিকের জন্য লিপিবদ্ধ হবে। অনুরূপ লেখা হবে তার লাদ ও পেশাব পরিমাণ সওয়াব। সে ঘোড়া যখনই তার রশি ছিড়ে একটি অথবা দু’টি ময়দান অতিক্রম করবে, তখনই তার পদক্ষেপ ও লাদ পরিমাণ সওয়াব তার মালিকের জন্য লিখিত হবে। অনুরূপ তার মালিক যদি তাকে কোন নদীর কিনারায় নিয়ে যায়, অতঃপর সে সেই নদী হতে পানি পান করে অথচ মালিকের পান করানোর ইচ্ছা থাকে না, তবুও আল্লাহ তা’আলা তার পান করা পানির সমপরিমাণ সওয়াব মালিকের জন্য লিপিবদ্ধ করে দেবেন।” জিজ্ঞাসা করা হল, ’হে আল্লাহর রাসূল! আর গাধা সম্পর্কে কি হবে?’ তিনি বললেন, “গাধার ব্যাপারে এই ব্যাপকার্থক একক আয়াতটি ছাড়া আমার উপর অন্য কিছু অবতীর্ণ হয়নি, ﴿فَمَنْ يَعْمَلْ مِثْقَالَ ذَرَّةٍ خَيْراً يَرَهُ وَمَنْ يَعْمَلْ مِثْقَالَ ذَرَّةٍ شَرّاً يَرَهُ ﴾ (الزلزلة: ٧، ٨) অর্থাৎ যে ব্যক্তি অণু-পরিমাণ সৎকর্ম করবে সে তাও (কিয়ামতে) প্রত্যক্ষ করবে এবং যে ব্যক্তি অণু-পরিমাণ অসৎকার্য করবে সে তাও (সেদিন) প্রত্যক্ষ করবে।” (সূরা যিলযাল ৭-৮ আয়াত) (বুখারী ২৩৭১, মুসলিম ৯৮৭নং, নাসাঈ, হাদিসের শব্দাবলী সহীহ মুসলিম শরীফের।)[১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>وَعَن أَبِي هُرَيرَةَ رضي الله عنه، قَالَ: قَالَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم: «قَالَ اللهُ - عَزَّ وَجَلَّ -: كُلُّ عَمَلِ ابْنِ آدَمَ لَهُ إِلاَّ الصِّيَام، فَإِنَّهُ لِي وَأَنَا أَجْزِي بِهِ، وَالصِّيَامُ جُنَّةٌ، فَإِذَا كَانَ يَومُ صَوْمِ أَحَدِكُمْ فَلاَ يَرْفُثْ وَلاَ يَصْخَبْ فَإِنْ سَابَّهُ أَحَدٌ أَوْ قَاتَلَهُ فَلْيَقُلْ: إنِّي صَائِمٌ . وَالَّذِي نَفْسُ مُحَمَّدٍ بِيَدِهِ لَخُلُوْفُ فَمِ الصَّائِمِ أَطْيَبُ عِنْدَ اللهِ مِنْ رِيحِ المِسْكِ . لِلصَّائِمِ فَرْحَتَانِ يَفْرَحُهُمَا: إِذَا أَفْطَرَ فَرِحَ بِفِطرِهِ، وَإِذَا لَقِيَ رَبَّهُ فَرِحَ بِصَوْمِهِ». متفقٌ عَلَيْهِ، وهذا لفظ روايةِ البُخَارِي.وفي روايةٍ لَهُ: «يَتْرُكُ طَعَامَهُ، وَشَرَابَهُ، وَشَهْوَتَهُ مِنْ أَجْلِي، الصِّيَامُ لِي وَأنَا أَجْزِي بِهِ، وَالحَسَنَةُ بِعَشْرِ أَمْثَالِهَا».وفي رواية لمسلم: «كُلُّ عَمَلِ ابْنِ آدَمَ يُضَاعَفُ، اَلْحَسَنَةُ بِعَشْرِ أَمْثَالِهَا إِلَى سَبْعِمِئَةِ ضِعْفٍ . قَالَ الله تَعَالَى: إِلاَّ الصَّوْمَ فَإِنَّهُ لِي وَأنَا أَجْزِي بِهِ؛ يَدَعُ شَهْوَتَهُ وَطَعَامَهُ مِنْ أَجْلِي. لِلصَّائِمِ فَرْحَتَانِ: فَرْحَةٌ عِنْدَ فِطْرِهِ، وَفَرْحَةٌ عِنْدَ لِقَاءِ رَبِّهِ . وَلَخُلُوفُ فِيهِ أَطْيَبُ عِنْدَ اللهِ مِنْ رِيحِ المِسْكِ».</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন, “মহান আল্লাহ বলেন, ’আদম সন্তানের প্রতিটি সৎকর্ম তার জন্যই; কিন্তু রোযা স্বতন্ত্র, তা আমারই জন্য, আর আমিই তার প্রতিদান দেব।’রোযা ঢাল স্বরূপঅতএব তোমাদের কেউ যেন রোযার দিনে অশ্লীল না বলে এবং হৈ-হট্টগোল না করে। আর যদি কেউ তাকে গালি-গালাজ করে অথবা তার সাথে লড়াই-ঝগড়া করে, তাহলে সে যেন বলে, ’আমি রোযা রেখেছি।’ সেই মহান সত্তার শপথ! যার হাতে মুহাম্মদের জীবন আছে, নিঃসন্দেহে রোজাদারের মুখের দুর্গন্ধ আল্লাহর কাছে মৃগনাভির সুগন্ধ অপেক্ষা বেশী উৎকৃষ্ট। রোজাদারের জন্য দু’টি আনন্দময় মুহূর্ত রয়েছে, তখন সে আনন্দিত হয়; (১) যখন সে ইফতার করে (ইফতারের জন্য সে আনন্দিত হয়)। আর (২) যখন সে তার প্রতিপালকের সঙ্গে সাক্ষাৎ করবে, স্বীয় রোযার জন্য সে আনন্দিত হবে।” (বুখারী ও মুসলিম, এই শব্দগুলি বুখারীর)[১] বুখারীর অন্য বর্ণনায় আছে, ’সে (রোজাদার) পানাহার ও যৌনাচার বর্জন করে একমাত্র আমারই জন্য। রোযা আমার জন্যই। আর আমি নিজে তার পুরস্কার দেব। আর প্রত্যেক নেকী দশগুণ বর্ধিত হয়।’ মুসলিমের এক বর্ণনায় আছে, “আদম সন্তানের প্রত্যেক সৎকর্ম কয়েকগুণ বর্ধিত করা হয়। একটি নেকী দশগুণ থেকে নিয়ে সাতশত গুণ পর্যন্ত বৃদ্ধি পায়। মহান আল্লাহ বলেন, ’কিন্তু রোযা ছাড়া। কেননা, তা আমার উদ্দেশ্যে (পালিত) হয়। আর আমি নিজেই তার পুরস্কার দেব। সে পানাহার ও কাম প্রবৃত্তি আমার (সন্তুষ্টি অর্জনের) উদ্দেশ্যেই বর্জন করে।’ রোজাদারের জন্য দু’টি আনন্দময় মুহূর্ত রয়েছে। একটি আনন্দ হল ইফতারের সময়, আর অপরটি তার প্রতিপালকের সাথে সাক্ষাৎকালে। আর নিশ্চয় তার মুখের গন্ধ আল্লাহর কাছে মৃগনাভির সুগন্ধ অপেক্ষা অধিক উৎকৃষ্ট।”</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>وَعَنْ أَبِي هُرَيرَةَ رضي الله عنه، عَنِ النَّبِيِّ صلى الله عليه وسلم، قَالَ: «مَنْ صَامَ رَمَضَانَ إِيمَاناً وَاحْتِسَاباً، غُفِرَ لَهُ مَا تَقَدَّمَ مِنْ ذَنْبِهِ» متفقٌ عَلَيْهِ</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>নবী (صلى الله عليه وسلم) বলেছেন, “যে ব্যক্তি ঈমান সহকারে নেকীর আশায় রমযানের রোযা পালন করে, তার অতীতের গুনাহসমূহ ক্ষমা করে দেওয়া হয়।” (বুখারী ও মুসলিম)[১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>وَعَنْ عَائِشَة رَضِيَ اللهُ عَنهَا، قَالَتْ: كَانَ رَسُولُ اللهِ صلى الله عليه وسلم صلى الله عليه وسلم إِذَا دَخَلَ العَشْرُ أَحْيَا اللَّيْلَ، وَأَيْقَظَ أَهْلَهُ، وَشَدَّ المِئْزَرَ . متفقٌ عَلَيْهِ</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, ’(রমযানের) শেষ দশক প্রবেশ করলে আল্লাহর রাসূল (صلى الله عليه وسلم) স্বয়ং রাতে জাগতেন এবং পরিবার-পরিজনদেরকেও জাগাতেন। আর (ইবাদতের জন্য) কোমর বেঁধে নিতেন।’ (বুখারী ও মুসলিম) [১]</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>عَن أَبِي هُرَيرَةَ رضي الله عنه، عَنِ النَّبِيِّ صلى الله عليه وسلم، قَالَ: «لاَ يَتَقَدَّمَنَّ أَحَدُكُم رَمَضَانَ بِصَوْمِ يَوْمٍ أَوْ يَوْمَيْنِ، إِلاَّ أَنْ يَكُونَ رَجُلٌ كَانَ يَصُومُ صَومَهُ، فَليَصُمْ ذَلِكَ اليَوْمَ». متفقٌ عَلَيْهِ</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>নবী (صلى الله عليه وسلم) বলেছেন, “তোমাদের কেউ যেন রমযান মাসের এক বা দু’দিন আগে (শা’বানের শেষে) রোযা পালন শুরু না করে। অবশ্য সেই ব্যক্তি রোযা রাখতে পারে, যে ঐ দিনে রোযা রাখতে অভ্যস্ত।” (বুখারী ও মুসলিম)[১]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
